--- a/projects/nas-sos-capstone/prework/1 System Requirements_10-26_v1.xlsx
+++ b/projects/nas-sos-capstone/prework/1 System Requirements_10-26_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\capstone_isd\projects\nas-sos-capstone\prework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_88D62115FA124B858FA1784A17227B36A8559A0C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5593055F-2D5C-43D7-B544-41D698BC2852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="6465" windowWidth="29655" windowHeight="7455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="330" yWindow="0" windowWidth="29655" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" r:id="rId1"/>
@@ -31756,6 +31756,6 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>